--- a/docs/onboarding/modele-onboarding-flotte.xlsx
+++ b/docs/onboarding/modele-onboarding-flotte.xlsx
@@ -107,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,9 +123,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -201,6 +198,101 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Pièces</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Toyota, Hyundai…</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Hilux, H1…</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>2018</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>1234 AB 01</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>N° de châssis (17 car.)</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>2.5 D-4D, essence…</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>en km</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>voir liste</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>ex : Dépôt Nord</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>nom du chauffeur</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Pièces</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Prénom Nom</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>+2250700000000</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>B, C, D…</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>JJ/MM/AAAA</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>remarques</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -846,56 +938,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Toyota, Hyundai…</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>Hilux, H1…</t>
-        </is>
-      </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>1234 AB 01</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>N° de châssis (17 car.)</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>2.5 D-4D, essence…</t>
-        </is>
-      </c>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
-          <t>en km</t>
-        </is>
-      </c>
-      <c r="H2" s="10" t="inlineStr">
-        <is>
-          <t>voir liste</t>
-        </is>
-      </c>
-      <c r="I2" s="10" t="inlineStr">
-        <is>
-          <t>ex : Dépôt Nord</t>
-        </is>
-      </c>
-      <c r="J2" s="10" t="inlineStr">
-        <is>
-          <t>nom du chauffeur</t>
-        </is>
-      </c>
+      <c r="A2" s="7" t="n"/>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
+      <c r="J2" s="7" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n"/>
@@ -1583,15 +1635,16 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="H3:H59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"TRANSPORT,CHANTIER,LIVRAISON,DIRECTION,AUTRE"</formula1>
     </dataValidation>
-    <dataValidation sqref="C3:C59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="C2:C59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>1980</formula1>
       <formula2>2030</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1645,31 +1698,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Prénom Nom</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>+2250700000000</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>B, C, D…</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>JJ/MM/AAAA</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>remarques</t>
-        </is>
-      </c>
+      <c r="A2" s="7" t="n"/>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n"/>
@@ -1969,5 +2003,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>